--- a/抖音来客诊断规则表A.xlsx
+++ b/抖音来客诊断规则表A.xlsx
@@ -1926,28 +1926,30 @@
       <c r="E21" s="16" t="inlineStr">
         <is>
           <t>1. 数据采集：采集诊断当次携程用户端该酒店全部在售房型及实时价格。
-2. 引流房型筛选：按价格由低到高排序，取最低的前两个价格档位；落在这两个价格档位内的全部同价房型均纳入，因此最终引流房型数量可以超过2个。
-3. 房型映射：使用已经确认的携程房型与抖音房型对应关系，确定每个引流房型在抖音来客中的对应适用房型。
-4. 存在性判断：逐个检查抖音“预售房型”中是否已经存在该适用房型。已存在对应预售房型时直接诊断通过，不再校验商品售卖时段、预售房型名称、房量房态—基础房量或房间数量。
-5. 缺失判断：不存在对应预售房型时，为该引流房型形成1条新增任务。
+2. 档位筛选：按价格由低到高排序，取携程最低价房型、第二低价格房型和最高价房型三个档位；落在同一价格档位内的全部同价房型均纳入，因此每档房型数量可以超过1个。
+3. 房型映射：使用已经确认的携程房型与抖音房型对应关系，确定每个档位房型在抖音来客中的对应适用房型。
+4. 存在性判断：逐个检查抖音“预售房型”中是否已经存在该适用房型。已存在时按原有规则逐个诊断（商品售卖时段、预售房型名称、房量房态—基础房量、房间数量），全部一致诊断通过。
+5. 缺失判断：不存在对应预售房型时，为该档位房型形成1条新增任务。
 6. 唯一性规则：同一个适用房型只允许创建1个预售房型，不允许重复创建。
-7. 任务粒度：一个缺失引流房型生成1条任务；多个缺失房型分别生成任务，不得合并。</t>
+7. 钟点房检查：检查预售房型中是否存在钟点房；不存在时形成1条确认提示任务，提示文案：“检测到预售管理中没有钟点房，需要与酒店确认并建议去抖音来客系统新增钟点房。”
+8. 任务粒度：一个缺失档位房型生成1条任务；多个缺失房型分别生成任务，不得合并。</t>
         </is>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
           <t>一、任务页面：
-1. 展示携程最低的前两个价格档位、每个档位内的全部房型名称及诊断当次实时价格，并标明当前任务对应的引流房型。
-2. 问题提示：“检测到价格最低的XX房型没有在预售房型中，是否根据携程完善预售房型？详情信息如下。”
-3. 详情展示：房型名称、商品售卖时段、适用房型、预售房型名称、房量房态—基础房量、房间数量。
-4. 辅助说明：“若确认以此信息补充预售房型，请点击【提交】即可开始填充。”
+1. 展示携程最低价、第二低价格、最高价三个档位及每档房型名称与诊断当次实时价格，并标明当前任务对应的档位房型。
+2. 问题提示：“检测到携程XX档位房型没有在预售房型中，是否根据携程完善预售房型？详情信息如下。”
+3. 钟点房缺失时单独形成提示任务：“检测到预售管理中没有钟点房，需要与酒店确认并建议去抖音来客系统新增钟点房。”
+4. 详情展示：房型名称、商品售卖时段、适用房型、预售房型名称、房量房态—基础房量、房间数量。
+5. 辅助说明：“若确认以此信息补充预售房型，请点击【提交】即可开始填充。”
 二、字段映射：
 1. 商品售卖时段=全日房。
-2. 适用房型=当前携程引流房型对应的抖音房型。
+2. 适用房型=当前携程档位房型对应的抖音房型。
 3. 预售房型名称=所选择的抖音适用房型名称。
 4. 房量房态—基础房量=限制数量。
 5. 房间数量=诊断当次从抖音“房价房态管理”采集到的该房型房量。
-6. 携程实时价格仅用于划分前两个价格档位、识别引流房型及向用户展示筛选依据，不写入预售房型字段。</t>
+6. 携程实时价格仅用于划分三个档位、识别档位房型及向用户展示筛选依据，不写入预售房型字段。</t>
         </is>
       </c>
       <c r="G21" s="16" t="inlineStr">
@@ -2007,13 +2009,16 @@
       </c>
       <c r="E22" s="21" t="inlineStr">
         <is>
-          <t>1. 诊断范围：AI逐个点击团购商品“查看”，读取商品搭配、实际售卖价格、商品名称、间夜数、不可入住日期、预约及入住规则。
-2. 预售房型覆盖：未来30天无节假日时，每个预售房型至少应有1个日常团购商品；不存在则形成新增日常团购任务。
-3. 未来30天有节假日时，仅取距离诊断日最近的1个节假日；每个预售房型分别检查日常团购和该节假日团购。两个都缺少时，在同一房型补充任务中展示两个可独立确认的新增方案；已有一个时只补另一个；两个都存在时覆盖通过。
-4. 一个团购商品只能搭配一个预售房型；同一预售房型可分别创建日常和节假日商品，但名称、价格必须不同。
-5. 实际售价：优先取商促价，无商促价时取非划线价，划线价不参与实际售价比较。设每晚基准P、间夜数N、抖音实际售价S、携程对比总价C=P×N；S≤C通过，S&gt;C形成价格修改任务。日常P取携程日常价；节假日P取最近节假日期间全部日期中的最低每晚价格。建议售价=P×N×95%。
-6. 商品名称：日常商品按“房型＋间夜数＋酒店免费特色＋酒店名称中包含的景区名称”；节假日商品按“【最近节假日】＋房型＋间夜数＋酒店免费特色＋酒店名称中包含的景区名称”。没有真实数据的组成项直接跳过，不得生成；不同商品名称不得完全相同。
-7. 同一商品同时存在价格和名称问题时，分别生成价格任务和名称任务，不得合并。</t>
+          <t>1. 覆盖要求：检查以下团购商品是否齐全——①携程最低价房型的“2天1晚”团购；②携程第二低价格房型的“三天两晚”和“2天1晚”两个团购；③携程最高价房型的“三天两晚”团购；④钟点房团购。
+2. 钟点房缺失提示：无钟点房团购时在任务中单独提示：“检测到团购管理中没有钟点房，需要与酒店确认并建议去抖音来客系统新增钟点房团购，方便为酒店引流。”由用户选择“去与酒店确认”或“暂不处理”。
+3. 其他房型缺失：按新增方案规则形成新增任务（商品搭配、价格、名称按公式预填，可独立确认）；部分缺失时只补缺失方案。
+4. 均已存在：按原有规则逐个诊断（商品搭配、实际售卖价格、名称、间夜数、不可入住日期、预约及入住规则）。
+5. 诊断范围：AI逐个点击团购商品“查看”，读取商品搭配、实际售卖价格、商品名称、间夜数、不可入住日期、预约及入住规则。
+6. 预售房型覆盖（节假日）：未来30天有节假日时，仅取距离诊断日最近的1个节假日；涉及预售房型分别检查日常团购和该节假日团购，缺失的按新增方案补充。
+7. 一个团购商品只能搭配一个预售房型；同一预售房型可分别创建日常和节假日商品，但名称、价格必须不同。
+8. 实际售价：优先取商促价，无商促价时取非划线价，划线价不参与实际售价比较。设每晚基准P、间夜数N、抖音实际售价S、携程对比总价C=P×N；S≤C通过，S&gt;C形成价格修改任务。日常P取携程日常价；节假日P取最近节假日期间全部日期中的最低每晚价格。建议售价=P×N×95%。
+9. 商品名称：日常商品按“房型＋间夜数＋酒店免费特色＋酒店名称中包含的景区名称”；节假日商品按“【最近节假日】＋房型＋间夜数＋酒店免费特色＋酒店名称中包含的景区名称”。没有真实数据的组成项直接跳过，不得生成；不同商品名称不得完全相同。
+10. 同一商品同时存在价格和名称问题时，分别生成价格任务和名称任务，不得合并。</t>
         </is>
       </c>
       <c r="F22" s="21" t="inlineStr">
@@ -2029,8 +2034,9 @@
 8. 套餐图：取携程对应物理房型图片。
 9. 不可入住日期：日常商品选择“节假日不可用”，并按抖音来客字段提供的节假日时间区间设置；节假日商品不选择“节假日不可用”，确保节假日可入住。
 10. 预约规则：需要提前预约、提前1天；取消规则沿用抖音默认；最早入住、最晚退房映射携程入住/退房时间。
-二、价格问题：展示商品、关联房型、间夜数、携程基准价、抖音实际售价、对比总价及建议售价。
-三、名称问题：展示当前名称、动态名称组成依据及建议名称。</t>
+二、钟点房团购缺失时，在任务中单独展示提示卡片：“检测到团购管理中没有钟点房，需要与酒店确认并建议去抖音来客系统新增钟点房团购，方便为酒店引流。”并提供处理意向选择（去与酒店确认/暂不处理）。
+三、价格问题：展示商品、关联房型、间夜数、携程基准价、抖音实际售价、对比总价及建议售价。
+四、名称问题：展示当前名称、动态名称组成依据及建议名称。</t>
         </is>
       </c>
       <c r="G22" s="21" t="inlineStr">

--- a/抖音来客诊断规则表A.xlsx
+++ b/抖音来客诊断规则表A.xlsx
@@ -2023,7 +2023,7 @@
       </c>
       <c r="F22" s="21" t="inlineStr">
         <is>
-          <t>一、缺少团购商品时，任务展示完整新增方案及所有待填字段：
+          <t>一、缺少团购商品时，任务开头提示：“识别到抖音来客团购缺失{房型}{间夜数}预售 / {房型}{间夜数}套餐，下面将进行补充。”（按本次缺失项生成），随后直接展示完整新增方案及所有待填字段：
 1. 商品品类：取“店铺管理/门店管理”中的门店品类，层级分隔符转换为“/”。
 2. 商品类型=预售券；商品售卖时段=全日房。
 3. 商品名称：按日常/节假日动态名称公式预填。
